--- a/data/trans_dic/P6906-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P6906-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño</t>
+          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,48; 26,21</t>
+          <t>8,35; 26,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,49; 27,4</t>
+          <t>10,68; 27,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,87; 37,98</t>
+          <t>12,29; 36,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,85; 32,71</t>
+          <t>9,63; 34,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 36,42</t>
+          <t>6,21; 35,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,51; 50,71</t>
+          <t>18,11; 52,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,3; 49,3</t>
+          <t>15,33; 48,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,32; 33,98</t>
+          <t>14,94; 32,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,51; 24,24</t>
+          <t>9,58; 23,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,76; 30,49</t>
+          <t>16,39; 31,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,99; 35,41</t>
+          <t>17,13; 36,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,17; 29,02</t>
+          <t>14,06; 29,98</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,85; 29,69</t>
+          <t>15,3; 29,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,08; 35,82</t>
+          <t>16,07; 34,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,33; 28,09</t>
+          <t>9,69; 27,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,83; 27,39</t>
+          <t>10,4; 26,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,08; 28,78</t>
+          <t>7,87; 28,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,35; 48,68</t>
+          <t>22,13; 48,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,7; 48,53</t>
+          <t>22,67; 48,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,47; 34,59</t>
+          <t>19,25; 34,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,33; 27,19</t>
+          <t>15,28; 27,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,13; 36,44</t>
+          <t>21,54; 36,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,86; 32,43</t>
+          <t>16,43; 31,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,41; 27,9</t>
+          <t>16,12; 27,29</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,22; 27,87</t>
+          <t>12,18; 28,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,0; 48,68</t>
+          <t>25,29; 47,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,28; 35,87</t>
+          <t>18,16; 35,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,15; 30,27</t>
+          <t>8,33; 30,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,15; 40,91</t>
+          <t>16,17; 43,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,01; 33,37</t>
+          <t>11,72; 34,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,42; 38,39</t>
+          <t>17,4; 40,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 32,26</t>
+          <t>6,02; 32,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,9; 31,23</t>
+          <t>16,17; 30,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,6; 39,01</t>
+          <t>22,59; 39,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20,07; 34,45</t>
+          <t>20,02; 33,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,05; 26,18</t>
+          <t>7,9; 26,45</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,02; 37,44</t>
+          <t>21,2; 36,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,53; 34,67</t>
+          <t>15,73; 36,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,39; 40,97</t>
+          <t>20,27; 39,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,86; 32,82</t>
+          <t>14,49; 32,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,55; 33,47</t>
+          <t>15,89; 33,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,86; 43,43</t>
+          <t>19,75; 43,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,55; 51,84</t>
+          <t>24,92; 50,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,07; 39,69</t>
+          <t>22,99; 39,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,33; 33,34</t>
+          <t>20,91; 33,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,39; 34,83</t>
+          <t>20,39; 34,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,89; 41,22</t>
+          <t>25,55; 41,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,97; 32,62</t>
+          <t>20,99; 33,06</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,65; 26,87</t>
+          <t>18,99; 26,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,88; 31,09</t>
+          <t>21,21; 30,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,25; 29,12</t>
+          <t>19,04; 28,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,76; 24,42</t>
+          <t>14,51; 24,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,67; 27,49</t>
+          <t>16,43; 28,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,69; 36,26</t>
+          <t>23,59; 36,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,65; 39,62</t>
+          <t>25,81; 38,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,18; 29,99</t>
+          <t>18,01; 29,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,33; 25,67</t>
+          <t>19,12; 25,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,65; 31,42</t>
+          <t>23,79; 31,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23,8; 31,32</t>
+          <t>23,44; 31,28</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,36; 26,11</t>
+          <t>18,49; 25,62</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño</t>
+          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6728; 20794</t>
+          <t>6621; 21217</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8035; 20983</t>
+          <t>8179; 21419</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7035; 20766</t>
+          <t>6720; 19990</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7016; 23293</t>
+          <t>6860; 24457</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2034; 11741</t>
+          <t>2003; 11527</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6342; 17375</t>
+          <t>6205; 17829</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4576; 14748</t>
+          <t>4585; 14631</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8925; 18581</t>
+          <t>8170; 17870</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10607; 27050</t>
+          <t>10688; 26744</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17471; 33801</t>
+          <t>18163; 34453</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13522; 29950</t>
+          <t>14489; 30859</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17838; 36531</t>
+          <t>17699; 37749</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23143; 43347</t>
+          <t>22338; 42891</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14760; 32887</t>
+          <t>14749; 31844</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9051; 27243</t>
+          <t>9399; 26502</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12132; 30671</t>
+          <t>11644; 30126</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4266; 15197</t>
+          <t>4156; 14851</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14191; 30912</t>
+          <t>14054; 30592</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12057; 26957</t>
+          <t>12596; 26866</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19218; 34150</t>
+          <t>19007; 33984</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30474; 54041</t>
+          <t>30380; 54400</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32818; 56593</t>
+          <t>33448; 56127</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25721; 49472</t>
+          <t>25066; 47522</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34570; 58795</t>
+          <t>33962; 57501</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13436; 30645</t>
+          <t>13393; 31774</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19886; 38729</t>
+          <t>20120; 37590</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20091; 39438</t>
+          <t>19959; 39476</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4504; 16734</t>
+          <t>4603; 16708</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7513; 19038</t>
+          <t>7526; 20455</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5834; 17679</t>
+          <t>6210; 18506</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11280; 24858</t>
+          <t>11264; 25949</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6686; 31259</t>
+          <t>5838; 31092</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>24881; 48865</t>
+          <t>25300; 48429</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28627; 51698</t>
+          <t>29939; 52006</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35050; 60175</t>
+          <t>34975; 58092</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12256; 39842</t>
+          <t>12019; 40259</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30183; 51317</t>
+          <t>29052; 49799</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12158; 27142</t>
+          <t>12310; 28304</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18029; 36221</t>
+          <t>17920; 35106</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15018; 33153</t>
+          <t>14643; 32878</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13773; 29641</t>
+          <t>14067; 30018</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12727; 27834</t>
+          <t>12661; 27615</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17548; 34257</t>
+          <t>16468; 33334</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23964; 41232</t>
+          <t>23887; 41077</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48115; 75226</t>
+          <t>47172; 74958</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29037; 49589</t>
+          <t>29036; 49658</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40001; 63689</t>
+          <t>39472; 63696</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42980; 66844</t>
+          <t>43022; 67758</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>88075; 126925</t>
+          <t>89686; 126337</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>68102; 101429</t>
+          <t>69182; 100999</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67365; 101921</t>
+          <t>66641; 100637</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50125; 82915</t>
+          <t>49279; 82439</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>36699; 60513</t>
+          <t>36169; 62153</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>50884; 77900</t>
+          <t>50686; 78378</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>57639; 85697</t>
+          <t>55820; 83491</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>64394; 106237</t>
+          <t>63793; 106128</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>133854; 177728</t>
+          <t>132408; 178065</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>127966; 169978</t>
+          <t>128695; 172629</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>134773; 177346</t>
+          <t>132743; 177122</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>127376; 181106</t>
+          <t>128239; 177729</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6906-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P6906-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,35; 26,74</t>
+          <t>8,51; 25,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,68; 27,97</t>
+          <t>10,53; 27,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,29; 36,56</t>
+          <t>12,33; 36,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 34,34</t>
+          <t>10,08; 34,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,21; 35,75</t>
+          <t>6,31; 35,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,11; 52,04</t>
+          <t>17,8; 51,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,33; 48,91</t>
+          <t>15,45; 48,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,94; 32,68</t>
+          <t>15,69; 33,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,58; 23,97</t>
+          <t>9,99; 24,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,39; 31,08</t>
+          <t>15,23; 30,09</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,13; 36,48</t>
+          <t>17,07; 36,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,06; 29,98</t>
+          <t>14,58; 30,32</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,3; 29,38</t>
+          <t>16,32; 30,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,07; 34,69</t>
+          <t>15,32; 34,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,69; 27,33</t>
+          <t>9,99; 28,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,4; 26,9</t>
+          <t>12,39; 29,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,87; 28,13</t>
+          <t>7,92; 27,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,13; 48,18</t>
+          <t>22,04; 47,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,67; 48,36</t>
+          <t>22,46; 47,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,25; 34,42</t>
+          <t>19,96; 35,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,28; 27,37</t>
+          <t>14,65; 26,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,54; 36,14</t>
+          <t>21,4; 36,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,43; 31,15</t>
+          <t>16,36; 31,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,12; 27,29</t>
+          <t>16,97; 28,66</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,18; 28,9</t>
+          <t>12,34; 29,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,29; 47,25</t>
+          <t>25,53; 48,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,16; 35,91</t>
+          <t>17,69; 34,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,33; 30,23</t>
+          <t>9,28; 29,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,17; 43,96</t>
+          <t>16,03; 41,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,72; 34,93</t>
+          <t>11,08; 32,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,4; 40,08</t>
+          <t>16,17; 39,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,02; 32,08</t>
+          <t>17,94; 37,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,17; 30,95</t>
+          <t>15,88; 29,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,59; 39,24</t>
+          <t>21,79; 38,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20,02; 33,26</t>
+          <t>20,67; 34,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,9; 26,45</t>
+          <t>16,68; 30,77</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,2; 36,34</t>
+          <t>21,91; 37,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,73; 36,16</t>
+          <t>16,29; 35,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,27; 39,71</t>
+          <t>20,13; 39,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,49; 32,54</t>
+          <t>15,31; 32,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,89; 33,9</t>
+          <t>15,13; 32,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,75; 43,08</t>
+          <t>18,99; 41,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,92; 50,44</t>
+          <t>26,66; 51,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,99; 39,54</t>
+          <t>24,44; 41,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,91; 33,23</t>
+          <t>21,18; 32,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,39; 34,88</t>
+          <t>20,56; 35,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,55; 41,23</t>
+          <t>25,38; 41,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,99; 33,06</t>
+          <t>22,04; 33,65</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,99; 26,75</t>
+          <t>18,68; 26,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,21; 30,96</t>
+          <t>21,5; 31,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,04; 28,75</t>
+          <t>19,45; 29,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,51; 24,28</t>
+          <t>15,29; 24,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,43; 28,24</t>
+          <t>16,67; 27,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,59; 36,48</t>
+          <t>23,1; 35,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,81; 38,6</t>
+          <t>26,98; 39,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,01; 29,96</t>
+          <t>23,65; 32,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,12; 25,72</t>
+          <t>19,21; 25,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,79; 31,91</t>
+          <t>23,55; 31,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23,44; 31,28</t>
+          <t>23,64; 31,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,49; 25,62</t>
+          <t>20,75; 27,36</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13436</t>
+          <t>14787</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12830</t>
+          <t>14173</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26266</t>
+          <t>28960</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6621; 21217</t>
+          <t>6748; 20238</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8179; 21419</t>
+          <t>8066; 21251</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6720; 19990</t>
+          <t>6743; 19754</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6860; 24457</t>
+          <t>7566; 25642</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2003; 11527</t>
+          <t>2033; 11398</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6205; 17829</t>
+          <t>6100; 17515</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4585; 14631</t>
+          <t>4620; 14635</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8170; 17870</t>
+          <t>9384; 20199</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10688; 26744</t>
+          <t>11151; 27120</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18163; 34453</t>
+          <t>16882; 33352</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14489; 30859</t>
+          <t>14441; 31279</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17699; 37749</t>
+          <t>19662; 40892</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19053</t>
+          <t>25618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26367</t>
+          <t>27986</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>45419</t>
+          <t>53604</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22338; 42891</t>
+          <t>23828; 44977</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14749; 31844</t>
+          <t>14062; 31284</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9399; 26502</t>
+          <t>9690; 27281</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11644; 30126</t>
+          <t>16481; 39537</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4156; 14851</t>
+          <t>4181; 14555</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14054; 30592</t>
+          <t>13993; 29898</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12596; 26866</t>
+          <t>12477; 26636</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19007; 33984</t>
+          <t>21443; 37631</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30380; 54400</t>
+          <t>29118; 53490</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33448; 56127</t>
+          <t>33242; 57183</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25066; 47522</t>
+          <t>24956; 47778</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33962; 57501</t>
+          <t>40801; 68915</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>12344</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18226</t>
+          <t>19232</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27498</t>
+          <t>31576</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13393; 31774</t>
+          <t>13563; 32206</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20120; 37590</t>
+          <t>20309; 38302</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19959; 39476</t>
+          <t>19445; 38442</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4603; 16708</t>
+          <t>6391; 20367</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7526; 20455</t>
+          <t>7458; 19491</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6210; 18506</t>
+          <t>5869; 17353</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11264; 25949</t>
+          <t>10471; 25308</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5838; 31092</t>
+          <t>12685; 26308</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25300; 48429</t>
+          <t>24850; 46766</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29939; 52006</t>
+          <t>28875; 50876</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34975; 58092</t>
+          <t>36100; 60859</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12019; 40259</t>
+          <t>23282; 42943</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22680</t>
+          <t>24689</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>31784</t>
+          <t>34664</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>54464</t>
+          <t>59353</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29052; 49799</t>
+          <t>30031; 51829</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12310; 28304</t>
+          <t>12749; 27507</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17920; 35106</t>
+          <t>17794; 34651</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14643; 32878</t>
+          <t>16548; 35297</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14067; 30018</t>
+          <t>13396; 28901</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12661; 27615</t>
+          <t>12169; 26690</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16468; 33334</t>
+          <t>17620; 34056</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23887; 41077</t>
+          <t>26230; 44020</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>47172; 74958</t>
+          <t>47773; 74164</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29036; 49658</t>
+          <t>29270; 50606</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39472; 63696</t>
+          <t>39206; 63524</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43022; 67758</t>
+          <t>47485; 72500</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64442</t>
+          <t>77437</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>89206</t>
+          <t>96056</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>153648</t>
+          <t>173494</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>89686; 126337</t>
+          <t>88246; 126617</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>69182; 100999</t>
+          <t>70136; 102828</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66641; 100637</t>
+          <t>68077; 101494</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49279; 82439</t>
+          <t>58875; 94842</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>36169; 62153</t>
+          <t>36686; 60996</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>50686; 78378</t>
+          <t>49624; 77038</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55820; 83491</t>
+          <t>58361; 85372</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>63793; 106128</t>
+          <t>81681; 111908</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>132408; 178065</t>
+          <t>133037; 179563</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>128695; 172629</t>
+          <t>127406; 169802</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>132743; 177122</t>
+          <t>133864; 175950</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>128239; 177729</t>
+          <t>151571; 199855</t>
         </is>
       </c>
     </row>
